--- a/src/attributions/attributions_ig_traj_73.xlsx
+++ b/src/attributions/attributions_ig_traj_73.xlsx
@@ -2137,10 +2137,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1113102384937421</v>
+        <v>0.2245905504691396</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -2149,10 +2149,10 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.01636927260969227</v>
+        <v>0.0172335929648189</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0893482582368655</v>
+        <v>-0.2797414549864706</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -2164,25 +2164,25 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05566710293441492</v>
+        <v>0.3263087609918314</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.02099855854309517</v>
+        <v>-0.01892699875143671</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.09760726711756632</v>
+        <v>-0.2650234781322075</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>-0</v>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.008362045617196508</v>
+        <v>-0.1051075779999233</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2203,43 +2203,43 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.008676848379950331</v>
+        <v>-0.1219748388124217</v>
       </c>
       <c r="X4" t="n">
-        <v>0.004340028097492126</v>
+        <v>-0.05998155594408982</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.02610766720867033</v>
+        <v>-0.06614081682891967</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.03281291651597838</v>
+        <v>-0.05273307269644276</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.005172486419582826</v>
+        <v>-0.08184419539554219</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ4" t="n">
         <v>-0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.004122720217828025</v>
+        <v>-0.006168849466169715</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
@@ -2257,106 +2257,106 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.01606908013989432</v>
+        <v>-0.0620239257091784</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.009558187960666216</v>
+        <v>-0.03928098147514957</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.126249051314047</v>
+        <v>0.515978654930348</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.01982093522319862</v>
+        <v>-0.1005117651041472</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.08606256971663089</v>
+        <v>-0.1752276447778177</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.03187298592046191</v>
+        <v>0.02963871177682685</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.0421311225835585</v>
+        <v>-0.0407710093832381</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.03981293404679091</v>
+        <v>-0.1308245722024932</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
         <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.04636833004909312</v>
+        <v>0.09286529975779004</v>
       </c>
       <c r="BN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
         <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.02047232979193178</v>
+        <v>0.1088086676755833</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0182817414874055</v>
+        <v>0.1709458458784759</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.02392069269616133</v>
+        <v>0.054168896463068</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
@@ -2365,16 +2365,16 @@
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.01400818106140688</v>
+        <v>-0.08678032820057535</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0.009197148926830592</v>
+        <v>-0.1570728068922795</v>
       </c>
       <c r="CA4" t="n">
         <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.02842497524408625</v>
+        <v>-0.0881903167799499</v>
       </c>
       <c r="CF4" t="n">
         <v>0</v>
@@ -2392,10 +2392,10 @@
         <v>0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.005411016177733139</v>
+        <v>-0.03912114872543162</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.04606493778585791</v>
+        <v>0.1811337357124211</v>
       </c>
       <c r="CJ4" t="n">
         <v>0</v>
@@ -2404,52 +2404,52 @@
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.01033097503792382</v>
+        <v>-0.2073080557140679</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.01403898243511722</v>
+        <v>0.09550080726113119</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.01560377511469216</v>
+        <v>0.1442403783744078</v>
       </c>
       <c r="CS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.02038419962829842</v>
+        <v>-0.0917889883480853</v>
       </c>
       <c r="CX4" t="n">
         <v>-0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.009478018091916712</v>
+        <v>-0.03819520271169663</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.04240461851821046</v>
+        <v>0.1639733798314676</v>
       </c>
       <c r="DB4" t="n">
         <v>-0</v>
@@ -2458,79 +2458,79 @@
         <v>-0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.02189501852186262</v>
+        <v>0.01363352883558573</v>
       </c>
       <c r="DG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.005422656666762696</v>
+        <v>-0.1344020223328125</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.07974676180458971</v>
+        <v>0.03723156715378143</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
       </c>
       <c r="DL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.01051193501313229</v>
+        <v>-0.0656550619748987</v>
       </c>
       <c r="DP4" t="n">
         <v>0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.01669597249913554</v>
+        <v>0.1265594144890717</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.01138294176387023</v>
+        <v>0.2147288427325979</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW4" t="n">
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.01509704943984092</v>
+        <v>-0.03079342066614882</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.01262820745371198</v>
+        <v>0.06551753580449415</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0.04141560984739803</v>
+        <v>-0.1041753443875814</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
@@ -2539,55 +2539,55 @@
         <v>-0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
         <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.01182112465370409</v>
+        <v>-0.1357164354768499</v>
       </c>
       <c r="EH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI4" t="n">
         <v>0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.005858412103696023</v>
+        <v>-0.08587357667628882</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.008785527510300506</v>
+        <v>0.1342304546684608</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.008971845080107555</v>
+        <v>0.02370831482355811</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.01444990997783941</v>
+        <v>-0.06929447566899696</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.04349415066224779</v>
+        <v>0.1525235249564215</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
         <v>0</v>
@@ -2596,10 +2596,10 @@
         <v>0</v>
       </c>
       <c r="EX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.02040934819080244</v>
+        <v>-0.0981649226205905</v>
       </c>
       <c r="EZ4" t="n">
         <v>-0</v>
@@ -2608,37 +2608,37 @@
         <v>0</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.005091301534146465</v>
+        <v>-0.06945140377026029</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.03867003881273349</v>
+        <v>0.163095939795342</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
         <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.01408762042128033</v>
+        <v>-0.1307126568613693</v>
       </c>
       <c r="FI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ4" t="n">
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.02471885702916216</v>
+        <v>-0.04894109303498006</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.01017443041838587</v>
+        <v>-0.04916471822367102</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
@@ -2647,52 +2647,52 @@
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>5.285006455389482e-05</v>
+        <v>0.04102018914647956</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
         <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.0079752439107405</v>
+        <v>0.07042473443166622</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.06289426336073492</v>
+        <v>0.1850940038153784</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
       </c>
       <c r="FW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.02446047871731042</v>
+        <v>0.01642180328711951</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
         <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0.009438942409479678</v>
+        <v>0.1427007719586141</v>
       </c>
       <c r="GE4" t="n">
         <v>0</v>
@@ -2701,87 +2701,87 @@
         <v>0</v>
       </c>
       <c r="GG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5986412522618729</v>
+        <v>0.5886634132636891</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4119290590772555</v>
+        <v>-0.6279797284885309</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.08428958501992513</v>
+        <v>-0.1024608890200818</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
         <v>-0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J5" t="n">
         <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3776762568002086</v>
+        <v>0.4973384543635065</v>
       </c>
       <c r="L5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2798223570391798</v>
+        <v>-0.6136431274817126</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1004297324232794</v>
+        <v>-0.1574763265224191</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.065950676470312</v>
+        <v>0.04494254906851385</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.06294594899757858</v>
+        <v>-0.04423193342521088</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.08728622689581868</v>
+        <v>-0.05422804580469766</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -2790,22 +2790,22 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1897325011232952</v>
+        <v>-0.0006802922213800049</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.04106135182657642</v>
+        <v>-0.06492230016773959</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.04105286842307232</v>
+        <v>0.04589654591428416</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>-0</v>
@@ -2814,19 +2814,19 @@
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.05988103969425758</v>
+        <v>0.1300740982973569</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.04182753144371142</v>
+        <v>-0.1259213594902213</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.03763824559632466</v>
+        <v>0.07310412110787927</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
@@ -2838,49 +2838,49 @@
         <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT5" t="n">
         <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.6956643754603489</v>
+        <v>0.5472907902247156</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.0841006876021041</v>
+        <v>-0.4013742733251794</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1153538756944155</v>
+        <v>-0.4290047096472393</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.05631704779675577</v>
+        <v>0.03613573118848425</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.1775933060814753</v>
+        <v>-0.09976098983489796</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.237143581580249</v>
+        <v>0.02288165679763798</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
@@ -2889,34 +2889,34 @@
         <v>-0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.04244816559507177</v>
+        <v>-0.1018873609442352</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.05350728388569553</v>
+        <v>0.1414773227970992</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.08103687636666876</v>
+        <v>0.04510527281261149</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
         <v>-0</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT5" t="n">
         <v>-0</v>
@@ -2925,46 +2925,46 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1949190517115665</v>
+        <v>0.1881669838891533</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.06742332803475437</v>
+        <v>-0.2579169622339412</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.01278015598554702</v>
+        <v>-0.04153295597795301</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC5" t="n">
         <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.1658560344705098</v>
+        <v>-0.3005103694935636</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.08538728480810066</v>
+        <v>0.3104001553948849</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.04161946339686588</v>
+        <v>0.00282870387467942</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ5" t="n">
         <v>-0</v>
@@ -2973,49 +2973,49 @@
         <v>0</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM5" t="n">
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0479265965241967</v>
+        <v>-0.2205035553359128</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.08506113238110852</v>
+        <v>0.3703274832489584</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.09785257939859811</v>
+        <v>0.06897065783995486</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
         <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU5" t="n">
         <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.1462468204866899</v>
+        <v>-0.3025082774886643</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.1146057093420463</v>
+        <v>0.3239624236735675</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.01077465540315156</v>
+        <v>0.0392134600558561</v>
       </c>
       <c r="DA5" t="n">
         <v>0</v>
@@ -3033,19 +3033,19 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.008602130870010638</v>
+        <v>-0.009588445268888151</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.1044161911424611</v>
+        <v>0.09354876377437599</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.1392338836606648</v>
+        <v>-0.07218459308082466</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK5" t="n">
         <v>-0</v>
@@ -3060,19 +3060,19 @@
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.1026976341413352</v>
+        <v>-0.1619677083706076</v>
       </c>
       <c r="DP5" t="n">
         <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.07348659150385613</v>
+        <v>0.2067894818002686</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.1059232308694603</v>
+        <v>-0.06227733371518729</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
@@ -3084,28 +3084,28 @@
         <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.01719980584098722</v>
+        <v>0.02982142455358049</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.01618827263212546</v>
+        <v>0.1608502530772576</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.02108720460874676</v>
+        <v>0.03678249568632329</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
         <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
         <v>-0</v>
@@ -3114,49 +3114,49 @@
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.06597407373793208</v>
+        <v>-0.2271001916579552</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.03870074916895523</v>
+        <v>0.2371269149285753</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.0947242540474757</v>
+        <v>0.0986275502017101</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
         <v>-0</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
         <v>-0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.131286339435391</v>
+        <v>-0.2649699574253926</v>
       </c>
       <c r="EQ5" t="n">
         <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.1303154485025055</v>
+        <v>0.1937749155617304</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.06387863580127351</v>
+        <v>0.05043598793166745</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
         <v>0</v>
@@ -3165,79 +3165,79 @@
         <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.1495962194866843</v>
+        <v>-0.3264262906442771</v>
       </c>
       <c r="EZ5" t="n">
         <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.1150252861303488</v>
+        <v>0.3717818993674187</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.02672185170445438</v>
+        <v>0.0116945225195828</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
         <v>0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
         <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.06138092164756817</v>
+        <v>-0.1460120265564379</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>-0.0793090373703577</v>
+        <v>-0.141649537397054</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.05118023515361843</v>
+        <v>-0.003400616079490973</v>
       </c>
       <c r="FL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN5" t="n">
         <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.00692276023581444</v>
+        <v>0.1823068580133239</v>
       </c>
       <c r="FR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.002281599328218854</v>
+        <v>0.3113724097366018</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.08857426759093699</v>
+        <v>-0.0193564244591495</v>
       </c>
       <c r="FU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW5" t="n">
         <v>0</v>
@@ -3246,78 +3246,78 @@
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.07327636196009232</v>
+        <v>-0.1569873241738392</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>-0.05487230190743134</v>
+        <v>0.2097592232781839</v>
       </c>
       <c r="GC5" t="n">
         <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.05443221429886995</v>
+        <v>0.05454487877326832</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.03602023102514559</v>
+        <v>0.01356887434434661</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.01755783661972684</v>
+        <v>-0.02963663190649131</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02101881342818472</v>
+        <v>0.08224104715644354</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.04526384842242909</v>
+        <v>-5.895403171953651e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.02959732634745329</v>
+        <v>-0.0309823237175659</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -3329,10 +3329,10 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01113641271901068</v>
+        <v>-0.001822697182248718</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3341,160 +3341,160 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.004404500425885263</v>
+        <v>-0.0156443697215547</v>
       </c>
       <c r="X6" t="n">
-        <v>0.007108281093310431</v>
+        <v>-0.0007519195539797655</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB6" t="n">
         <v>-0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.03106560508257816</v>
+        <v>-0.01507023255148224</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.03108934301769707</v>
+        <v>-0.05400211362081756</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.008473338477993017</v>
+        <v>-0.01162586840379892</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.004105679381175024</v>
+        <v>0.007296417379774755</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.01036920006294871</v>
+        <v>-0.008166776562336411</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.004189025897504569</v>
+        <v>-0.009895015091491779</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.1161752890976263</v>
+        <v>0.1105477450746666</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.01556129241602457</v>
+        <v>-0.03370054405971747</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.01280307775267524</v>
+        <v>-0.02914001703796764</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC6" t="n">
         <v>-0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.001080287649780843</v>
+        <v>-0.005284523182256904</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF6" t="n">
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.05903608910374847</v>
+        <v>-0.02103132653572864</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.01455911847064702</v>
+        <v>-0.01501643067054104</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.04434958393897587</v>
+        <v>0.02068557021334866</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.02576758511984803</v>
+        <v>0.04896258563170287</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.02023019232016935</v>
+        <v>0.0296215838159061</v>
       </c>
       <c r="BR6" t="n">
         <v>-0</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT6" t="n">
         <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.01746081641935811</v>
+        <v>0.02489988430199242</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3503,13 +3503,13 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.007946024448589811</v>
+        <v>-0.004596885726028553</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.008567971247036609</v>
+        <v>-0.01856466048063837</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>0</v>
@@ -3521,7 +3521,7 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.01129315236388879</v>
+        <v>-0.01514431589129336</v>
       </c>
       <c r="CF6" t="n">
         <v>0</v>
@@ -3530,52 +3530,52 @@
         <v>-0</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.001486153915044772</v>
+        <v>-0.002238811077805981</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.01252870330369078</v>
+        <v>0.02901478543447028</v>
       </c>
       <c r="CJ6" t="n">
         <v>-0</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL6" t="n">
         <v>-0</v>
       </c>
       <c r="CM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.01913051438702313</v>
+        <v>-0.04249749144086465</v>
       </c>
       <c r="CO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.01311961830183533</v>
+        <v>0.05285949294085143</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.01179245564006036</v>
+        <v>0.01826405480088623</v>
       </c>
       <c r="CS6" t="n">
         <v>0</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.001420712343933146</v>
+        <v>-0.01664950744587473</v>
       </c>
       <c r="CX6" t="n">
         <v>-0</v>
@@ -3584,16 +3584,16 @@
         <v>0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.0005336657076146879</v>
+        <v>-0.004001577274973955</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.01211301484659912</v>
+        <v>0.0270864876050255</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD6" t="n">
         <v>0</v>
@@ -3602,19 +3602,19 @@
         <v>-0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.01351446073566557</v>
+        <v>-0.02532339714352079</v>
       </c>
       <c r="DG6" t="n">
         <v>-0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.0002410484299758846</v>
+        <v>-0.001369584527608249</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.01233508065340037</v>
+        <v>-0.009897396960830866</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
@@ -3623,28 +3623,28 @@
         <v>-0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.01049915821442943</v>
+        <v>-0.01102665929253045</v>
       </c>
       <c r="DP6" t="n">
         <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.008849987586112022</v>
+        <v>-0.004104398852657199</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.008288948221510741</v>
+        <v>0.03784527241170112</v>
       </c>
       <c r="DT6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU6" t="n">
         <v>-0</v>
@@ -3653,10 +3653,10 @@
         <v>-0</v>
       </c>
       <c r="DW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.001166698752888318</v>
+        <v>-0.007099601900349493</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
@@ -3665,16 +3665,16 @@
         <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.02246493027338766</v>
+        <v>0.01906252059770655</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.01017580032887849</v>
+        <v>0.0247249617603582</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
         <v>-0</v>
@@ -3683,7 +3683,7 @@
         <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.003395871046923613</v>
+        <v>-0.01466634940575647</v>
       </c>
       <c r="EH6" t="n">
         <v>-0</v>
@@ -3692,10 +3692,10 @@
         <v>-0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.003767584662902779</v>
+        <v>-0.01277999801675456</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.00228506883281636</v>
+        <v>0.01325760726454671</v>
       </c>
       <c r="EL6" t="n">
         <v>-0</v>
@@ -3707,25 +3707,25 @@
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.005516271774458079</v>
+        <v>0.003190590820261824</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.01991012250326264</v>
+        <v>-0.009137614767274664</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.03996727963814431</v>
+        <v>0.01610753929073874</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
         <v>0</v>
@@ -3737,61 +3737,61 @@
         <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.003165091661319877</v>
+        <v>-0.02240366521826879</v>
       </c>
       <c r="EZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.0002161809570979792</v>
+        <v>-0.009416410394990801</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.01530234643799567</v>
+        <v>0.02275789445146927</v>
       </c>
       <c r="FD6" t="n">
         <v>-0</v>
       </c>
       <c r="FE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF6" t="n">
         <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.007922619688496255</v>
+        <v>-0.03229423502306705</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.01826171117387398</v>
+        <v>0.03494286080576232</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.01253690840660516</v>
+        <v>0.008216651590029229</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
       </c>
       <c r="FN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.004531307146505034</v>
+        <v>0.006395362918492483</v>
       </c>
       <c r="FR6" t="n">
         <v>-0</v>
@@ -3800,28 +3800,28 @@
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.01085670806087258</v>
+        <v>-0.004982193848887145</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.007816934890331223</v>
+        <v>-0.019214162878404</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
       </c>
       <c r="FW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.03255326651356494</v>
+        <v>-0.0001555898231422302</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
         <v>-0</v>
@@ -3830,10 +3830,10 @@
         <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.00918470230154623</v>
+        <v>0.02228405911437461</v>
       </c>
       <c r="GE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF6" t="n">
         <v>-0</v>
@@ -3847,7 +3847,7 @@
         <v>-0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2459746722487689</v>
+        <v>0.07067879475506818</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -3856,7 +3856,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.08713150743578238</v>
+        <v>-0.03330068199285312</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3868,22 +3868,22 @@
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.04168610737136819</v>
+        <v>-0.01178497123110995</v>
       </c>
       <c r="J7" t="n">
         <v>-0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1404824007379721</v>
+        <v>0.1096793966118031</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1652702597236167</v>
+        <v>-0.03440318974000655</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3892,16 +3892,16 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.06165881878056265</v>
+        <v>-0.008976724685949355</v>
       </c>
       <c r="S7" t="n">
         <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.06129406771759127</v>
+        <v>-0.01837758258128145</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
@@ -3910,52 +3910,52 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.01378476877306833</v>
+        <v>-0.03324083381191831</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z7" t="n">
         <v>-0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001738458985069238</v>
+        <v>-0.000259621307454299</v>
       </c>
       <c r="AB7" t="n">
         <v>-0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.07443812469307173</v>
+        <v>-0.01790540603384359</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.03047071463553089</v>
+        <v>-0.0172502777289218</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.01329807954943694</v>
+        <v>-0.001246855997366685</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.03715596855115226</v>
+        <v>0.01109707063857555</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
@@ -3964,37 +3964,37 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.01746919060106185</v>
+        <v>-0.008130371640646212</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.009585993129639651</v>
+        <v>-0.004896771283563321</v>
       </c>
       <c r="AT7" t="n">
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.355678636923181</v>
+        <v>0.1174421528331357</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1306721496472585</v>
+        <v>-0.01730689015047101</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -4003,22 +4003,22 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.0122807421198491</v>
+        <v>0.01607244701878479</v>
       </c>
       <c r="BC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.03622883637770248</v>
+        <v>-0.007276808368435785</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.1558507539109598</v>
+        <v>-0.02486147776336645</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4027,70 +4027,70 @@
         <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.0366995335259075</v>
+        <v>-0.01403169646263799</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.01391843690041354</v>
+        <v>0.02007669873710258</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1518953939020629</v>
+        <v>0.04974840621967527</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.02853713879733118</v>
+        <v>0.02067309001931731</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.09872751426209114</v>
+        <v>0.02627113855003172</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.008125470899939825</v>
+        <v>-0.01459018495697277</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
         <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.008484394657369474</v>
+        <v>-0.009185020823893175</v>
       </c>
       <c r="CD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.05891302046568019</v>
+        <v>-0.02440459437475567</v>
       </c>
       <c r="CF7" t="n">
         <v>-0</v>
@@ -4099,10 +4099,10 @@
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0137059411044905</v>
+        <v>0.01013870846627213</v>
       </c>
       <c r="CI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ7" t="n">
         <v>-0</v>
@@ -4111,13 +4111,13 @@
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.04305985158655939</v>
+        <v>0.01676735094581751</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.05569626577400773</v>
+        <v>-0.04646159246672409</v>
       </c>
       <c r="CO7" t="n">
         <v>-0</v>
@@ -4126,10 +4126,10 @@
         <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.07954487852159771</v>
+        <v>0.0038675887773704</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,13 +4138,13 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>-0.001415124789539469</v>
+        <v>0.02471237062913068</v>
       </c>
       <c r="CV7" t="n">
         <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.05917854045254058</v>
+        <v>-0.02630676823008959</v>
       </c>
       <c r="CX7" t="n">
         <v>0</v>
@@ -4153,10 +4153,10 @@
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.02230942218505974</v>
+        <v>0.005545567035709431</v>
       </c>
       <c r="DA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB7" t="n">
         <v>0</v>
@@ -4165,22 +4165,22 @@
         <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.03638606203696341</v>
+        <v>0.01525449526628144</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.183072004849217</v>
+        <v>-0.012405846585206</v>
       </c>
       <c r="DG7" t="n">
         <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.07267545983124768</v>
+        <v>-0.01172640413492861</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
@@ -4189,124 +4189,124 @@
         <v>0</v>
       </c>
       <c r="DL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0.0229147838507533</v>
+        <v>-0.01895077677401585</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.01950696808827701</v>
+        <v>-0.02264120831157956</v>
       </c>
       <c r="DP7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.02845885425079861</v>
+        <v>0.01705981738755336</v>
       </c>
       <c r="DS7" t="n">
         <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV7" t="n">
-        <v>-0.03024102486856457</v>
+        <v>-0.03138623132055982</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.03905937057695569</v>
+        <v>0.005442458981955463</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
         <v>-0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.01701530719206031</v>
+        <v>0.007414690682883128</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.01639276344484292</v>
+        <v>-0.002474116176888522</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.007071275818588289</v>
+        <v>-0.02699411120548571</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.05275255301825654</v>
+        <v>0.002659725622204637</v>
       </c>
       <c r="EK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
         <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.05360658777996983</v>
+        <v>0.009868669389653625</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.06025600523777321</v>
+        <v>0.0003669020242259555</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER7" t="n">
         <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.02771469801407632</v>
+        <v>0.01185585793425768</v>
       </c>
       <c r="ET7" t="n">
         <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.02799096677860627</v>
+        <v>0.006940507201375869</v>
       </c>
       <c r="EX7" t="n">
         <v>0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.07069512274761008</v>
+        <v>-0.03029053058209621</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
@@ -4315,10 +4315,10 @@
         <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.01262209790980907</v>
+        <v>0.002163020298862385</v>
       </c>
       <c r="FC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD7" t="n">
         <v>-0</v>
@@ -4327,22 +4327,22 @@
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.02310023632048263</v>
+        <v>0.01592981462742072</v>
       </c>
       <c r="FG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.06369245122282419</v>
+        <v>-0.01985826504988541</v>
       </c>
       <c r="FI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.02416980572618913</v>
+        <v>0.0009458335274698825</v>
       </c>
       <c r="FL7" t="n">
         <v>0</v>
@@ -4351,16 +4351,16 @@
         <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.05786065531483138</v>
+        <v>0.05538482077544141</v>
       </c>
       <c r="FP7" t="n">
         <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.04783974733515053</v>
+        <v>0.01380407456557645</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
@@ -4369,10 +4369,10 @@
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.04253508229130467</v>
+        <v>-0.0104200256021914</v>
       </c>
       <c r="FU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV7" t="n">
         <v>-0</v>
@@ -4381,13 +4381,13 @@
         <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.004003616412608803</v>
+        <v>0.002389699519896546</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.09788864276522836</v>
+        <v>-0.005503973555596936</v>
       </c>
       <c r="GA7" t="n">
         <v>0</v>
@@ -4399,16 +4399,16 @@
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.02729222136481018</v>
+        <v>-0.003061614280155124</v>
       </c>
     </row>
     <row r="8">
@@ -4985,22 +4985,22 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.9902934886520319</v>
+        <v>0.1671206064971996</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6083535485096003</v>
+        <v>0.01334469092059048</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01914859909648012</v>
+        <v>-0.1344247068657388</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
         <v>-0</v>
@@ -5012,16 +5012,16 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6966959777764108</v>
+        <v>0.1360193141234372</v>
       </c>
       <c r="L9" t="n">
         <v>-0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5492530157738214</v>
+        <v>-0.1069159642225654</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.124197046078617</v>
+        <v>-0.2867330910382553</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -5030,7 +5030,7 @@
         <v>-0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -5039,16 +5039,16 @@
         <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1914773165275352</v>
+        <v>0.05518191104161885</v>
       </c>
       <c r="U9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1159059077172937</v>
+        <v>-0.05654310522445988</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.1265623777486824</v>
+        <v>-0.04272304199502253</v>
       </c>
       <c r="X9" t="n">
         <v>-0</v>
@@ -5057,7 +5057,7 @@
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -5066,22 +5066,22 @@
         <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.2000759035049972</v>
+        <v>-0.008827427481345657</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.08442144588912326</v>
+        <v>-0.09724808902341556</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.006960826195590351</v>
+        <v>-0.2284120385502826</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>-0</v>
@@ -5090,19 +5090,19 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.04941591015400918</v>
+        <v>0.06180160675540226</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.0663806176617201</v>
+        <v>-0.01815489712139716</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.0491502602900863</v>
+        <v>-0.004433673385364728</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
@@ -5120,43 +5120,43 @@
         <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.02361329123419</v>
+        <v>0.1913912320282856</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.0826469997582186</v>
+        <v>0.1440242856416975</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.3138534717017393</v>
+        <v>-0.4064351652532956</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
         <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.1631446221788011</v>
+        <v>-0.01121971280578208</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.1925857844298986</v>
+        <v>-0.1018256192615565</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.3955795916934759</v>
+        <v>-0.0296888114222194</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,22 +5174,22 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.2387508130482871</v>
+        <v>0.1237751788327635</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.1287039767629226</v>
+        <v>0.03987246027746767</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.1540863925724819</v>
+        <v>0.06230428887913398</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
@@ -5201,22 +5201,22 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.5336043272632739</v>
+        <v>0.2230242299707514</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0.04533787356158973</v>
+        <v>-0.04075536877595107</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.04622649616738751</v>
+        <v>-0.06645708245072798</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB9" t="n">
         <v>0</v>
@@ -5228,16 +5228,16 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.2334652111175453</v>
+        <v>-0.03345550769284875</v>
       </c>
       <c r="CF9" t="n">
         <v>0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.08885658518154019</v>
+        <v>0.02072840742727091</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.07760133371261423</v>
+        <v>0.0709332095868226</v>
       </c>
       <c r="CI9" t="n">
         <v>-0</v>
@@ -5255,19 +5255,19 @@
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.04499575432953829</v>
+        <v>-0.03152885150227679</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.2557542429433442</v>
+        <v>0.186425880239053</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.1295890579533202</v>
+        <v>0.222070445036047</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
@@ -5276,28 +5276,28 @@
         <v>-0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.1899180798568895</v>
+        <v>-0.005829414065294324</v>
       </c>
       <c r="CX9" t="n">
         <v>-0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.1444052808267127</v>
+        <v>0.036037092315548</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.05961201610739962</v>
+        <v>0.09676127350634721</v>
       </c>
       <c r="DA9" t="n">
         <v>0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
         <v>-0</v>
@@ -5306,52 +5306,52 @@
         <v>-0</v>
       </c>
       <c r="DE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.060996097380529</v>
+        <v>0.009499673334578773</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.153718533328127</v>
+        <v>-0.0167326178198261</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.07521704935034143</v>
+        <v>-0.03261519518186091</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
         <v>-0</v>
       </c>
       <c r="DL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN9" t="n">
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.1508441164153921</v>
+        <v>-0.1029232157712292</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.04317295892305266</v>
+        <v>-0.01344704698962182</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.102863666675874</v>
+        <v>0.09864580479575424</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
       </c>
       <c r="DT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU9" t="n">
         <v>-0</v>
@@ -5360,28 +5360,28 @@
         <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.03472344841028626</v>
+        <v>-0.04061267688643277</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.003304315542576621</v>
+        <v>0.02815436542129012</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.09759906736368064</v>
+        <v>-0.003528605399129827</v>
       </c>
       <c r="EB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC9" t="n">
         <v>0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
         <v>-0</v>
@@ -5390,16 +5390,16 @@
         <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.08904704937759876</v>
+        <v>0.08670103830329112</v>
       </c>
       <c r="EH9" t="n">
         <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.07981779929539468</v>
+        <v>0.03416567650068102</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.06851007480949828</v>
+        <v>0.005971950398550005</v>
       </c>
       <c r="EK9" t="n">
         <v>-0</v>
@@ -5414,19 +5414,19 @@
         <v>0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.2033615670525341</v>
+        <v>-0.06169242458140992</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
-        <v>-0.1797379552451721</v>
+        <v>-0.04264925477829169</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.09418288959268022</v>
+        <v>0.01323657516784925</v>
       </c>
       <c r="ET9" t="n">
         <v>-0</v>
@@ -5438,28 +5438,28 @@
         <v>0</v>
       </c>
       <c r="EW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX9" t="n">
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.1948731720675186</v>
+        <v>-0.03659271673759216</v>
       </c>
       <c r="EZ9" t="n">
         <v>0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.1291542105371431</v>
+        <v>0.03220764371993749</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.05380067859656947</v>
+        <v>0.06393219713061001</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
@@ -5468,85 +5468,85 @@
         <v>0</v>
       </c>
       <c r="FG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.0570770362935147</v>
+        <v>-0.03057155814352785</v>
       </c>
       <c r="FI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.09271166366306888</v>
+        <v>0.005775897841872746</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.0471883107622686</v>
+        <v>0.04964093836032445</v>
       </c>
       <c r="FL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM9" t="n">
         <v>-0</v>
       </c>
       <c r="FN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO9" t="n">
         <v>0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.04660044002048164</v>
+        <v>0.04117082356967398</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>-0.1424038178040424</v>
+        <v>0.04741438842549706</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.05429284176821481</v>
+        <v>-0.0422148076033733</v>
       </c>
       <c r="FU9" t="n">
         <v>-0</v>
       </c>
       <c r="FV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW9" t="n">
         <v>0</v>
       </c>
       <c r="FX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.09966755966976777</v>
+        <v>0.07628410988887108</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.06353037509891524</v>
+        <v>-0.06407829563650885</v>
       </c>
       <c r="GC9" t="n">
         <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5554,25 +5554,25 @@
         <v>-0</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.5211905024176086</v>
+        <v>-0.2604900447398871</v>
       </c>
       <c r="C10" t="n">
         <v>-0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4600812834771902</v>
+        <v>0.1588355289936803</v>
       </c>
       <c r="E10" t="n">
-        <v>0.08697179546070925</v>
+        <v>0.06627638934010209</v>
       </c>
       <c r="F10" t="n">
         <v>-0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.01531248036258747</v>
+        <v>-0.03493685245406371</v>
       </c>
       <c r="I10" t="n">
         <v>-0</v>
@@ -5581,25 +5581,25 @@
         <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3542268647501196</v>
+        <v>-0.24806493296238</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4255386808446055</v>
+        <v>0.3126725020956789</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2077171185061532</v>
+        <v>0.2611023743039474</v>
       </c>
       <c r="O10" t="n">
         <v>-0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.006673581939415725</v>
+        <v>-0.01360117078538202</v>
       </c>
       <c r="R10" t="n">
         <v>-0</v>
@@ -5608,16 +5608,16 @@
         <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1062768610997849</v>
+        <v>-0.1053917448291031</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.06960374259662537</v>
+        <v>0.1357498857365417</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1206106311832569</v>
+        <v>0.1082936523752335</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -5626,25 +5626,25 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.02265124125742549</v>
+        <v>-0.003534584358234692</v>
       </c>
       <c r="AA10" t="n">
         <v>-0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.11394643726438</v>
+        <v>0.07908990439106184</v>
       </c>
       <c r="AD10" t="n">
         <v>-0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.03172321722560068</v>
+        <v>0.03573000107861063</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0214633181599455</v>
+        <v>0.05553311438967663</v>
       </c>
       <c r="AG10" t="n">
         <v>-0</v>
@@ -5653,7 +5653,7 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>4.463373662594965e-05</v>
+        <v>-0.0107592436903827</v>
       </c>
       <c r="AJ10" t="n">
         <v>-0</v>
@@ -5662,16 +5662,16 @@
         <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.07447546844076242</v>
+        <v>-0.1023065961338179</v>
       </c>
       <c r="AM10" t="n">
         <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.01848174245948132</v>
+        <v>0.01555455716229873</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.009787114670644111</v>
+        <v>-0.04563692942901772</v>
       </c>
       <c r="AP10" t="n">
         <v>-0</v>
@@ -5680,52 +5680,52 @@
         <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.0274470154739487</v>
+        <v>-0.005801147763474215</v>
       </c>
       <c r="AS10" t="n">
         <v>-0</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0.7032640576837625</v>
+        <v>-0.3098807712446069</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.2144211636796164</v>
+        <v>0.04921295395269741</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.05075656747113952</v>
+        <v>0.3112872048716194</v>
       </c>
       <c r="AY10" t="n">
         <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0.005284724662324559</v>
+        <v>0.06848614242681159</v>
       </c>
       <c r="BB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.05133539032295208</v>
+        <v>0.03741837690644237</v>
       </c>
       <c r="BE10" t="n">
         <v>-0</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.1189106872671105</v>
+        <v>0.1054352124271421</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.3570271463164268</v>
+        <v>0.1913740159563738</v>
       </c>
       <c r="BH10" t="n">
         <v>-0</v>
@@ -5734,79 +5734,79 @@
         <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.01160317061323772</v>
+        <v>-0.01917270746716562</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL10" t="n">
         <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>-0.1220860299193349</v>
+        <v>0.05683069988083932</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>-0.01848507362261284</v>
+        <v>0.04259596766827232</v>
       </c>
       <c r="BP10" t="n">
-        <v>-0.1090068451665048</v>
+        <v>0.06575184336529809</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.008929135288122203</v>
+        <v>0.0155244964764051</v>
       </c>
       <c r="BT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU10" t="n">
         <v>0</v>
       </c>
       <c r="BV10" t="n">
-        <v>-0.3528554348479592</v>
+        <v>-0.2285802142785853</v>
       </c>
       <c r="BW10" t="n">
         <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.06524209439530641</v>
+        <v>0.224205691861099</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.01218772080609661</v>
+        <v>0.1681422040779795</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.02787896129696874</v>
+        <v>0.02896788093640736</v>
       </c>
       <c r="CC10" t="n">
         <v>-0</v>
       </c>
       <c r="CD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.1204189618794778</v>
+        <v>0.1244912618283854</v>
       </c>
       <c r="CF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG10" t="n">
-        <v>-0.07968826096860093</v>
+        <v>-0.06980537390598129</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.02685507980382685</v>
+        <v>-0.01984929191449194</v>
       </c>
       <c r="CI10" t="n">
         <v>0</v>
@@ -5815,7 +5815,7 @@
         <v>0</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.02431802138254559</v>
+        <v>0.04888097784731068</v>
       </c>
       <c r="CL10" t="n">
         <v>-0</v>
@@ -5824,43 +5824,43 @@
         <v>-0</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.03866424635403713</v>
+        <v>0.04787737507653822</v>
       </c>
       <c r="CO10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.07014170954409521</v>
+        <v>-0.2553462400747573</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.05003942050669247</v>
+        <v>-0.2668578246654216</v>
       </c>
       <c r="CR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS10" t="n">
         <v>0</v>
       </c>
       <c r="CT10" t="n">
-        <v>-0.1384515634793308</v>
+        <v>-0.0882297942781612</v>
       </c>
       <c r="CU10" t="n">
         <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.08420698809787834</v>
+        <v>0.1171014061345012</v>
       </c>
       <c r="CX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY10" t="n">
-        <v>-0.1036757469254532</v>
+        <v>-0.07807502507494496</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.01516591067152148</v>
+        <v>-0.03139985055021671</v>
       </c>
       <c r="DA10" t="n">
         <v>-0</v>
@@ -5869,52 +5869,52 @@
         <v>-0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.01724326617036775</v>
+        <v>0.03941889555917027</v>
       </c>
       <c r="DD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE10" t="n">
         <v>-0</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.1289772284911508</v>
+        <v>0.04973821692881756</v>
       </c>
       <c r="DG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH10" t="n">
-        <v>-0.07639867137688872</v>
+        <v>-0.01922370758368636</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.001641272199852879</v>
+        <v>0.03001385874011659</v>
       </c>
       <c r="DJ10" t="n">
         <v>-0</v>
       </c>
       <c r="DK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.00173120142416804</v>
+        <v>0.03910145722921488</v>
       </c>
       <c r="DM10" t="n">
         <v>0</v>
       </c>
       <c r="DN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.111621362478616</v>
+        <v>0.03724600265710145</v>
       </c>
       <c r="DP10" t="n">
         <v>0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0.03834872562179056</v>
+        <v>-0.1609601465740041</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.02280193681712595</v>
+        <v>0.03455095387368287</v>
       </c>
       <c r="DS10" t="n">
         <v>-0</v>
@@ -5923,52 +5923,52 @@
         <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>-0.1003962671823795</v>
+        <v>-0.05407470442908244</v>
       </c>
       <c r="DV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.03088082622601701</v>
+        <v>-0.02154062135697995</v>
       </c>
       <c r="DY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.01861282425683023</v>
+        <v>-0.07003592721237202</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.1562861729904459</v>
+        <v>-0.06975517757988897</v>
       </c>
       <c r="EB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC10" t="n">
         <v>0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0.025844833150511</v>
+        <v>0.009791274767427223</v>
       </c>
       <c r="EE10" t="n">
         <v>0</v>
       </c>
       <c r="EF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.004107308648371153</v>
+        <v>0.04734809008970246</v>
       </c>
       <c r="EH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>-0.1160306214702122</v>
+        <v>0.05730234286607136</v>
       </c>
       <c r="EJ10" t="n">
-        <v>-0.04665702504934502</v>
+        <v>-0.04745296162429025</v>
       </c>
       <c r="EK10" t="n">
         <v>0</v>
@@ -5977,25 +5977,25 @@
         <v>0</v>
       </c>
       <c r="EM10" t="n">
-        <v>-0.0092137011275173</v>
+        <v>0.05458782263952949</v>
       </c>
       <c r="EN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.08843319084262564</v>
+        <v>0.07677952420664678</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>-0.101516291299534</v>
+        <v>-0.04907499078989742</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.059649153404067</v>
+        <v>0.04002842316669137</v>
       </c>
       <c r="ET10" t="n">
         <v>0</v>
@@ -6004,25 +6004,25 @@
         <v>0</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.1367889586809393</v>
+        <v>0.04311978572629875</v>
       </c>
       <c r="EW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX10" t="n">
         <v>0</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.09399629029966639</v>
+        <v>0.1280958320430268</v>
       </c>
       <c r="EZ10" t="n">
         <v>0</v>
       </c>
       <c r="FA10" t="n">
-        <v>-0.1021841206678143</v>
+        <v>-0.114052323099904</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.002717068037618394</v>
+        <v>-0.03590144513552909</v>
       </c>
       <c r="FC10" t="n">
         <v>0</v>
@@ -6031,52 +6031,52 @@
         <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.02533518739367402</v>
+        <v>0.04975818837655044</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
         <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.03642097539331091</v>
+        <v>0.1405316620028864</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.06712023769060674</v>
+        <v>0.02751774935806399</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.07608050273526262</v>
+        <v>-0.1182155600826867</v>
       </c>
       <c r="FL10" t="n">
         <v>0</v>
       </c>
       <c r="FM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.01567484933819318</v>
+        <v>0.104143319748234</v>
       </c>
       <c r="FO10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP10" t="n">
         <v>0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.04287984118655629</v>
+        <v>-0.2331251746971449</v>
       </c>
       <c r="FR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.01637631518362845</v>
+        <v>-0.2310397988835655</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.06058358872389323</v>
+        <v>-0.03706111394022756</v>
       </c>
       <c r="FU10" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
         <v>0</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.02141883979298275</v>
+        <v>-0.1020594919017729</v>
       </c>
       <c r="FX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.1007802826019581</v>
+        <v>0.050635679117473</v>
       </c>
       <c r="GA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.05359488476569588</v>
+        <v>-0.0498423286547099</v>
       </c>
       <c r="GC10" t="n">
         <v>-0</v>
@@ -6109,13 +6109,13 @@
         <v>0</v>
       </c>
       <c r="GE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>-0.03314262247724926</v>
+        <v>0.04452931759914346</v>
       </c>
       <c r="GG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="11">
@@ -6123,19 +6123,19 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>1.10862526780012</v>
+        <v>0.3492191912302745</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6368148046853399</v>
+        <v>-0.2099677712066941</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2124409656842587</v>
+        <v>0.08547646298202324</v>
       </c>
       <c r="F11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>-0</v>
@@ -6144,25 +6144,25 @@
         <v>-0</v>
       </c>
       <c r="I11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1.015585757381994</v>
+        <v>0.407864863467565</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5642291729972219</v>
+        <v>-0.2860481121260791</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2718813836223437</v>
+        <v>0.06128020403830426</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P11" t="n">
         <v>-0</v>
@@ -6174,73 +6174,73 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2232398133688986</v>
+        <v>0.09481792813630618</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.03028339658074397</v>
+        <v>-0.0169224201988118</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1570843131775306</v>
+        <v>-0.06324864869794745</v>
       </c>
       <c r="X11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.2061183731767285</v>
+        <v>0.005786178255519269</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.05967274617896651</v>
+        <v>-0.1380964382721727</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.03616333881688029</v>
+        <v>0.01857824711055777</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.05898550724823656</v>
+        <v>0.05763217262088446</v>
       </c>
       <c r="AM11" t="n">
         <v>-0</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0.1103366840008159</v>
+        <v>-0.06646426713873052</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.06280634383043369</v>
+        <v>0.03053834522212621</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
@@ -6255,19 +6255,19 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.8720305289332277</v>
+        <v>0.3410517404828407</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0.2659231175178626</v>
+        <v>-0.1793204726537218</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.1379228208810876</v>
+        <v>-0.1334445391274258</v>
       </c>
       <c r="AY11" t="n">
         <v>-0</v>
@@ -6276,25 +6276,25 @@
         <v>-0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.1618137667481048</v>
+        <v>-0.008806636843452984</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>-0.1809473919744104</v>
+        <v>-0.06454693824996444</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.2727326677987407</v>
+        <v>0.04865604946763047</v>
       </c>
       <c r="BH11" t="n">
         <v>0</v>
@@ -6303,28 +6303,28 @@
         <v>-0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL11" t="n">
         <v>-0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.06555510665968664</v>
+        <v>-0.02095347805515525</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.07005404146727212</v>
+        <v>-0.01264200194234992</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.2457816206908688</v>
+        <v>0.01714217808450596</v>
       </c>
       <c r="BQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR11" t="n">
         <v>0</v>
@@ -6336,127 +6336,127 @@
         <v>-0</v>
       </c>
       <c r="BU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.4579082619126053</v>
+        <v>0.239852454465165</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>-0.06974144536733207</v>
+        <v>-0.07556704305817318</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.09499345356795505</v>
+        <v>0.006267444469844638</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
         <v>0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.2435359954115327</v>
+        <v>-0.1120611010323043</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.09594845508729634</v>
+        <v>0.1064675020747003</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.02389754809075514</v>
+        <v>-0.04725564577035549</v>
       </c>
       <c r="CI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
         <v>0</v>
       </c>
       <c r="CL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM11" t="n">
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.03444061475073653</v>
+        <v>-0.09507735708728043</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>-0.1873564629464247</v>
+        <v>0.2133171729947863</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.2576060345571643</v>
+        <v>-0.001307411045819431</v>
       </c>
       <c r="CR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS11" t="n">
         <v>-0</v>
       </c>
       <c r="CT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
         <v>-0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.2454154665839983</v>
+        <v>-0.107094574565862</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.1450740503812486</v>
+        <v>0.1131956901328311</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.03820442932408943</v>
+        <v>-0.04588552871302791</v>
       </c>
       <c r="DA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC11" t="n">
         <v>-0</v>
       </c>
       <c r="DD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.1156735330179239</v>
+        <v>-0.09663816156019744</v>
       </c>
       <c r="DG11" t="n">
         <v>-0</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.09940004028282566</v>
+        <v>0.03499401803326942</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.02609288273199181</v>
+        <v>-0.03133976715053908</v>
       </c>
       <c r="DJ11" t="n">
         <v>-0</v>
@@ -6471,19 +6471,19 @@
         <v>0</v>
       </c>
       <c r="DN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.04751506116156382</v>
+        <v>-0.06023592783031261</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0.2283716106507426</v>
+        <v>0.02140136002244015</v>
       </c>
       <c r="DR11" t="n">
-        <v>-0.1330282622277837</v>
+        <v>-0.06776884978277295</v>
       </c>
       <c r="DS11" t="n">
         <v>-0</v>
@@ -6492,85 +6492,85 @@
         <v>-0</v>
       </c>
       <c r="DU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV11" t="n">
         <v>0</v>
       </c>
       <c r="DW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.1899103384884921</v>
+        <v>-0.03589098679305638</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>-0.0933137311655166</v>
+        <v>-0.07036028788985277</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.04661832227035996</v>
+        <v>-0.08812263283060773</v>
       </c>
       <c r="EB11" t="n">
         <v>0</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.2378368866421187</v>
+        <v>-0.0806450643016826</v>
       </c>
       <c r="EH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.1774196217578836</v>
+        <v>0.09373938230895422</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.1878575924236002</v>
+        <v>0.001552104257160784</v>
       </c>
       <c r="EK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL11" t="n">
         <v>-0</v>
       </c>
       <c r="EM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.2449664270648726</v>
+        <v>-0.04359423568816508</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.106910635415193</v>
+        <v>0.01596306744814808</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.005738555773019365</v>
+        <v>-0.007667333338827885</v>
       </c>
       <c r="ET11" t="n">
         <v>-0</v>
       </c>
       <c r="EU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV11" t="n">
         <v>0</v>
@@ -6579,46 +6579,46 @@
         <v>-0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.2490821254234058</v>
+        <v>-0.1357952582005317</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.1121319645984503</v>
+        <v>0.1294623178486706</v>
       </c>
       <c r="FB11" t="n">
-        <v>-0.02389402593412945</v>
+        <v>-0.04783928528722655</v>
       </c>
       <c r="FC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.07361216981117942</v>
+        <v>0.1092537934136798</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.1720489007890382</v>
+        <v>0.1163838930733285</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.09243840454485389</v>
+        <v>0.0108276266097732</v>
       </c>
       <c r="FL11" t="n">
         <v>-0</v>
@@ -6630,22 +6630,22 @@
         <v>0</v>
       </c>
       <c r="FO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.09138497393770739</v>
+        <v>-0.07775918709688182</v>
       </c>
       <c r="FR11" t="n">
         <v>-0</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.02802209169793045</v>
+        <v>0.03055917473623383</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.08655610899224749</v>
+        <v>0.1374647770506577</v>
       </c>
       <c r="FU11" t="n">
         <v>0</v>
@@ -6654,22 +6654,22 @@
         <v>0</v>
       </c>
       <c r="FW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX11" t="n">
         <v>0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.008894823968667732</v>
+        <v>-0.1107925384229649</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
-        <v>-0.1216370278129555</v>
+        <v>0.05322260471293419</v>
       </c>
       <c r="GC11" t="n">
         <v>0</v>
@@ -6681,10 +6681,10 @@
         <v>-0</v>
       </c>
       <c r="GF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6692,49 +6692,49 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.6066138665529329</v>
+        <v>0.3807820340654174</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3170313451784009</v>
+        <v>-0.2166479685224378</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.08819419162418775</v>
+        <v>0.02007161171591568</v>
       </c>
       <c r="F12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
         <v>-0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5308203455018886</v>
+        <v>0.4473875402622344</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3194733189280368</v>
+        <v>-0.3062861523254922</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1351840295587689</v>
+        <v>-0.03068389123140634</v>
       </c>
       <c r="O12" t="n">
         <v>-0</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -6746,70 +6746,70 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1436642418041592</v>
+        <v>0.07869695684674488</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.009895618936870978</v>
+        <v>-0.01279102809863453</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1437861102506199</v>
+        <v>-0.07465366819173219</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1407657325925685</v>
+        <v>0.01278376918761865</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.02032552770039113</v>
+        <v>-0.1520031360495961</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.04508699667666013</v>
+        <v>0.002327987784743708</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.005942071012516868</v>
+        <v>0.06645953486357144</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.05987088096231129</v>
+        <v>-0.02139946459225725</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.06215676234881465</v>
+        <v>0.01403581705347425</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
@@ -6818,25 +6818,25 @@
         <v>-0</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.4998375727761785</v>
+        <v>0.3210454171555405</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.06507844702840632</v>
+        <v>-0.1363902410142125</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.1615230236700083</v>
+        <v>-0.2327632974733389</v>
       </c>
       <c r="AY12" t="n">
         <v>-0</v>
@@ -6845,55 +6845,55 @@
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>-0</v>
       </c>
       <c r="BC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.07449554751060181</v>
+        <v>0.02138835128388342</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.1494946969177984</v>
+        <v>-0.1027317160026049</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.1467073819784359</v>
+        <v>0.05820320194190012</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.09079010993690093</v>
+        <v>0.005022245023769021</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.02872359178941541</v>
+        <v>0.0139936136326582</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.2994612261803915</v>
+        <v>0.06318197040361669</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
         <v>0</v>
@@ -6908,16 +6908,16 @@
         <v>0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.2280461807480862</v>
+        <v>0.2206748959362733</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.01764160848282272</v>
+        <v>-0.07823107685749912</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.1192189373331396</v>
+        <v>-0.05453925343409906</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -6926,31 +6926,31 @@
         <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD12" t="n">
         <v>0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.145398603114674</v>
+        <v>-0.1114502659063819</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.03226544850955268</v>
+        <v>0.1133101793382598</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.007207931263310892</v>
+        <v>-0.01806941047266914</v>
       </c>
       <c r="CI12" t="n">
         <v>0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK12" t="n">
         <v>0</v>
@@ -6962,49 +6962,49 @@
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.05566592721864749</v>
+        <v>-0.1065199178747483</v>
       </c>
       <c r="CO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.1593827258296742</v>
+        <v>0.2188033307139344</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.1668808896215442</v>
+        <v>0.02148898570983873</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
       </c>
       <c r="CT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.1315285444038893</v>
+        <v>-0.0996666408760883</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.06527734924100229</v>
+        <v>0.1221363595651216</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.008612991262216886</v>
+        <v>-0.01694012108829439</v>
       </c>
       <c r="DA12" t="n">
         <v>-0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC12" t="n">
         <v>-0</v>
@@ -7016,16 +7016,16 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.07057669978353451</v>
+        <v>-0.06085233060121768</v>
       </c>
       <c r="DG12" t="n">
         <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.03880797028120846</v>
+        <v>0.06651746498230642</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.01634738492385569</v>
+        <v>-0.11759905433696</v>
       </c>
       <c r="DJ12" t="n">
         <v>-0</v>
@@ -7040,133 +7040,133 @@
         <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.03775590361102826</v>
+        <v>-0.08853451104429802</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0.1857822695911832</v>
+        <v>0.06229906027689888</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.03164784836880533</v>
+        <v>-0.05470485032011335</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.09657142041081633</v>
+        <v>-0.009622544868604855</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.008685243720313818</v>
+        <v>0.03135301319073351</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.01918259206261722</v>
+        <v>-0.04498946350094256</v>
       </c>
       <c r="EB12" t="n">
         <v>0</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
         <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.1473573092622562</v>
+        <v>-0.05970403657173984</v>
       </c>
       <c r="EH12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI12" t="n">
-        <v>-0.1192650212984031</v>
+        <v>-0.1493788905232494</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.1271803764202674</v>
+        <v>-0.000938839984379442</v>
       </c>
       <c r="EK12" t="n">
         <v>0</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.1381069298003292</v>
+        <v>-0.03631177220413784</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.06555399373771405</v>
+        <v>0.007382017311736983</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.008333981484709135</v>
+        <v>-0.008249043636606744</v>
       </c>
       <c r="ET12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
       </c>
       <c r="EW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX12" t="n">
         <v>0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.1353040288955496</v>
+        <v>-0.129525931582738</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.03563599420892002</v>
+        <v>0.137592608166012</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.01661037309829315</v>
+        <v>-0.02163514356195747</v>
       </c>
       <c r="FC12" t="n">
         <v>0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
@@ -7175,19 +7175,19 @@
         <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.05455321339319882</v>
+        <v>0.1039702661337421</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.08401326600909939</v>
+        <v>0.1027798161950255</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.04209106255096625</v>
+        <v>-0.0174826823846701</v>
       </c>
       <c r="FL12" t="n">
         <v>-0</v>
@@ -7196,31 +7196,31 @@
         <v>-0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
         <v>0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.02353570179717874</v>
+        <v>-0.1399923383578674</v>
       </c>
       <c r="FR12" t="n">
         <v>-0</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.06770084483129152</v>
+        <v>0.1531073321864995</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0.02810309528155342</v>
+        <v>0.1861776906465886</v>
       </c>
       <c r="FU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW12" t="n">
         <v>-0</v>
@@ -7229,19 +7229,19 @@
         <v>0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.03254595730502925</v>
+        <v>-0.08127289807776153</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.1242832640566904</v>
+        <v>0.0435281503489037</v>
       </c>
       <c r="GC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD12" t="n">
         <v>-0</v>
@@ -7250,10 +7250,10 @@
         <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,22 +7261,22 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>1.564438317047245</v>
+        <v>0.05745599301583969</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.4801806277184326</v>
+        <v>-0.02590105445308199</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1890452435384416</v>
+        <v>0.0112972159680771</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.494708805700207</v>
+        <v>-0.01066196075769661</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -7288,22 +7288,22 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1.209981519368658</v>
+        <v>0.0735930183929842</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.4204410705780985</v>
+        <v>-0.02847828199191605</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0.09785050839096103</v>
+        <v>-0.01084505550691432</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.3328633595427843</v>
+        <v>-0.01951156469030927</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -7315,103 +7315,103 @@
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2165332750795366</v>
+        <v>0.01589166105053721</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.07499926032030499</v>
+        <v>0.0135990355748754</v>
       </c>
       <c r="V13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1776313878391281</v>
+        <v>0.0001266281378650464</v>
       </c>
       <c r="X13" t="n">
         <v>-0</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.07331923528952451</v>
+        <v>0.001400895438430193</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.2790322122890453</v>
+        <v>0.01041331561347701</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.001372259844958498</v>
+        <v>-0.008624261698537368</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.07150099419593633</v>
+        <v>-0.01689549369844816</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0.138787305884505</v>
+        <v>-0.01200551347666687</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.08811771915752263</v>
+        <v>0.01256675353500063</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0.1706905907885532</v>
+        <v>-0.002314740945130653</v>
       </c>
       <c r="AN13" t="n">
         <v>-0</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.04069368815832248</v>
+        <v>0.01507825910887135</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0.08947823088425422</v>
+        <v>-0.001436946400744978</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.09545887715339</v>
+        <v>0.05474654998758541</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0.1998562410680262</v>
+        <v>0.004110785839688999</v>
       </c>
       <c r="AW13" t="n">
         <v>-0</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.2856314659454346</v>
+        <v>0.002849001121785768</v>
       </c>
       <c r="AY13" t="n">
         <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>-0.5199470463582111</v>
+        <v>0.001951834748664035</v>
       </c>
       <c r="BA13" t="n">
         <v>0</v>
@@ -7423,106 +7423,106 @@
         <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.3989955449727013</v>
+        <v>-0.008205966054106317</v>
       </c>
       <c r="BE13" t="n">
-        <v>-0.2692374958422595</v>
+        <v>-0.02189973047129874</v>
       </c>
       <c r="BF13" t="n">
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.2923483248587809</v>
+        <v>-0.01113204251499955</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0.1528470980650614</v>
+        <v>-0.003571505361928833</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL13" t="n">
         <v>-0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.3263471204865697</v>
+        <v>0.001225130292445639</v>
       </c>
       <c r="BN13" t="n">
-        <v>-0.1298346154554442</v>
+        <v>0.003084474661151424</v>
       </c>
       <c r="BO13" t="n">
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.08789999925109804</v>
+        <v>0.01362437251510696</v>
       </c>
       <c r="BQ13" t="n">
         <v>-0</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0.04669709556558666</v>
+        <v>-0.003103863388017901</v>
       </c>
       <c r="BS13" t="n">
         <v>-0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.4914415285149547</v>
+        <v>0.03656278799798156</v>
       </c>
       <c r="BW13" t="n">
-        <v>-0.4279927126647993</v>
+        <v>0.007611094177827162</v>
       </c>
       <c r="BX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.1249258509080047</v>
+        <v>0.004107768333408052</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
       </c>
       <c r="CA13" t="n">
-        <v>-0.1579569588365553</v>
+        <v>9.989758170983501e-05</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
         <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.3186821127089485</v>
+        <v>-0.01861200595439398</v>
       </c>
       <c r="CF13" t="n">
-        <v>-0.03421977780409369</v>
+        <v>0.008119027513747787</v>
       </c>
       <c r="CG13" t="n">
         <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.07194510508707196</v>
+        <v>-0.0020721209313867</v>
       </c>
       <c r="CI13" t="n">
         <v>-0</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.1530111888540693</v>
+        <v>0.005226449569253167</v>
       </c>
       <c r="CK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL13" t="n">
         <v>-0</v>
@@ -7531,52 +7531,52 @@
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.137263232489205</v>
+        <v>-0.02172582499881515</v>
       </c>
       <c r="CO13" t="n">
-        <v>-0.06240121999471192</v>
+        <v>0.003519176254257037</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.02892581498849759</v>
+        <v>0.01181232477103921</v>
       </c>
       <c r="CR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.179538368998953</v>
+        <v>-0.004250211249512125</v>
       </c>
       <c r="CT13" t="n">
         <v>0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV13" t="n">
         <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.3033212719705656</v>
+        <v>-0.01945559927809472</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0.07449594305099544</v>
+        <v>0.007371895705223045</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.1344011694904067</v>
+        <v>-0.002468733617308145</v>
       </c>
       <c r="DA13" t="n">
         <v>0</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.1580844449782692</v>
+        <v>0.006865930737869303</v>
       </c>
       <c r="DC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD13" t="n">
         <v>0</v>
@@ -7585,106 +7585,106 @@
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.3536724259028195</v>
+        <v>-0.002860137173110163</v>
       </c>
       <c r="DG13" t="n">
-        <v>-0.006204648792383641</v>
+        <v>0.01488465688681556</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>-0.060259988363143</v>
+        <v>-0.03979473952379899</v>
       </c>
       <c r="DJ13" t="n">
         <v>-0</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.0210118468540431</v>
+        <v>0.01199799611243325</v>
       </c>
       <c r="DL13" t="n">
         <v>-0</v>
       </c>
       <c r="DM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN13" t="n">
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.05649437299007992</v>
+        <v>-0.008776076508668006</v>
       </c>
       <c r="DP13" t="n">
-        <v>-0.1114526293266669</v>
+        <v>-6.793050063084797e-05</v>
       </c>
       <c r="DQ13" t="n">
         <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.08830062848053702</v>
+        <v>-0.009437012027808063</v>
       </c>
       <c r="DS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.08112079857415852</v>
+        <v>0.006490892045839106</v>
       </c>
       <c r="DU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW13" t="n">
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.3829707278212361</v>
+        <v>-0.02244463841185462</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.08988040317818283</v>
+        <v>-4.403199705817956e-05</v>
       </c>
       <c r="DZ13" t="n">
         <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.02139334406246612</v>
+        <v>0.00247428768261656</v>
       </c>
       <c r="EB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.01022777002649513</v>
+        <v>-0.02048388370197648</v>
       </c>
       <c r="ED13" t="n">
         <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.2094215133517111</v>
+        <v>-0.008441536777363194</v>
       </c>
       <c r="EH13" t="n">
-        <v>-0.0751992598559786</v>
+        <v>0.003533661049596536</v>
       </c>
       <c r="EI13" t="n">
         <v>-0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.02883386057580396</v>
+        <v>0.002207337432006904</v>
       </c>
       <c r="EK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.1823335743545391</v>
+        <v>-0.0002448950276274382</v>
       </c>
       <c r="EM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN13" t="n">
         <v>-0</v>
@@ -7693,22 +7693,22 @@
         <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.2395092040907817</v>
+        <v>-0.008533557126157753</v>
       </c>
       <c r="EQ13" t="n">
-        <v>-0.07809687534093654</v>
+        <v>0.001909824818183563</v>
       </c>
       <c r="ER13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.2093576233575279</v>
+        <v>0.005299179517855515</v>
       </c>
       <c r="ET13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.1584953785762921</v>
+        <v>0.0006711035245595779</v>
       </c>
       <c r="EV13" t="n">
         <v>0</v>
@@ -7717,52 +7717,52 @@
         <v>-0</v>
       </c>
       <c r="EX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.3011160281508934</v>
+        <v>-0.02280699265463884</v>
       </c>
       <c r="EZ13" t="n">
-        <v>-0.04327345722886523</v>
+        <v>0.006209481599814425</v>
       </c>
       <c r="FA13" t="n">
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.09248276279494379</v>
+        <v>-0.002809870182389821</v>
       </c>
       <c r="FC13" t="n">
         <v>-0</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.1662274786517847</v>
+        <v>0.004646773800656188</v>
       </c>
       <c r="FE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.06651316368909085</v>
+        <v>0.00744946017355361</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.07865828543062567</v>
+        <v>0.0123539241673098</v>
       </c>
       <c r="FJ13" t="n">
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.2314182112156442</v>
+        <v>0.01597884408655009</v>
       </c>
       <c r="FL13" t="n">
         <v>-0</v>
       </c>
       <c r="FM13" t="n">
-        <v>-0.04436717279907224</v>
+        <v>-0.01088224271086708</v>
       </c>
       <c r="FN13" t="n">
         <v>-0</v>
@@ -7771,28 +7771,28 @@
         <v>0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.01515436951711765</v>
+        <v>-0.01551417556859531</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.2668790984387312</v>
+        <v>-0.01077427603043528</v>
       </c>
       <c r="FS13" t="n">
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.0250451623023922</v>
+        <v>0.01897746818861833</v>
       </c>
       <c r="FU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV13" t="n">
-        <v>-0.006270869217737728</v>
+        <v>0.002178207851813701</v>
       </c>
       <c r="FW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX13" t="n">
         <v>0</v>
@@ -7801,28 +7801,28 @@
         <v>-0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.1298720510504627</v>
+        <v>-0.02301280348783624</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0.1569764348696804</v>
+        <v>-0.001161001891423945</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC13" t="n">
         <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE13" t="n">
-        <v>-0.04847252923683373</v>
+        <v>-0.003977507845417367</v>
       </c>
       <c r="GF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -7830,61 +7830,61 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.2043756583830827</v>
+        <v>0.5649541793306214</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.04386629843022957</v>
+        <v>0.0518395392227451</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1423386399395476</v>
+        <v>-0.3580925591703785</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H14" t="n">
         <v>-0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1741362742858704</v>
+        <v>0.7361786698378121</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.001209294562646114</v>
+        <v>-0.04057470249584846</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1026009948832638</v>
+        <v>-0.5174631300721676</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.01802108781063306</v>
+        <v>0.1877041745446287</v>
       </c>
       <c r="U14" t="n">
         <v>-0</v>
@@ -7893,16 +7893,16 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.0197006392103806</v>
+        <v>-0.09562567772941262</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.002195803080451526</v>
+        <v>-0.1374899761708116</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" t="n">
         <v>-0</v>
@@ -7911,19 +7911,19 @@
         <v>-0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.008892809872176093</v>
+        <v>0.01696368162247134</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.01689364405237849</v>
+        <v>-0.3536527136521438</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.008008990558974898</v>
+        <v>-0.01867562931029375</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
@@ -7938,52 +7938,52 @@
         <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.01095924671996771</v>
+        <v>0.1395487148108705</v>
       </c>
       <c r="AM14" t="n">
         <v>-0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.002654918504226958</v>
+        <v>-0.02745115041707313</v>
       </c>
       <c r="AP14" t="n">
-        <v>-0.04410392544052684</v>
+        <v>-0.0923696882900155</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR14" t="n">
         <v>-0</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.1259539729745685</v>
+        <v>0.9867073690744402</v>
       </c>
       <c r="AV14" t="n">
         <v>-0</v>
       </c>
       <c r="AW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.002764515257635965</v>
+        <v>-0.3110455220739778</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0.08132505891032485</v>
+        <v>-0.4353066529618462</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
         <v>-0</v>
@@ -7992,7 +7992,7 @@
         <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.03707386583091455</v>
+        <v>-0.1900642321771885</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
@@ -8001,10 +8001,10 @@
         <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.04524203987361435</v>
+        <v>-0.03981455944538928</v>
       </c>
       <c r="BH14" t="n">
-        <v>-0.03998331147352147</v>
+        <v>0.04475565787948887</v>
       </c>
       <c r="BI14" t="n">
         <v>0</v>
@@ -8013,55 +8013,55 @@
         <v>-0</v>
       </c>
       <c r="BK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL14" t="n">
         <v>0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.0207085311600753</v>
+        <v>0.203735501876187</v>
       </c>
       <c r="BN14" t="n">
         <v>-0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.02067480022039475</v>
+        <v>0.1205295419064986</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.00818180190937441</v>
+        <v>-0.03536935871282771</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
         <v>-0</v>
       </c>
       <c r="BT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.0656928213542245</v>
+        <v>0.4883827610786289</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY14" t="n">
-        <v>-0.007350013076157419</v>
+        <v>-0.07704506397963284</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0.02898002076486948</v>
+        <v>-0.2842484709845898</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB14" t="n">
         <v>-0</v>
@@ -8073,7 +8073,7 @@
         <v>0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.03897308934490779</v>
+        <v>-0.2097487506088369</v>
       </c>
       <c r="CF14" t="n">
         <v>-0</v>
@@ -8082,13 +8082,13 @@
         <v>-0</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.005626518451781404</v>
+        <v>0.05739987348089028</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.01774283698306015</v>
+        <v>0.09289972855996258</v>
       </c>
       <c r="CJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK14" t="n">
         <v>0</v>
@@ -8100,7 +8100,7 @@
         <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.001975866403378715</v>
+        <v>-0.3816493044427596</v>
       </c>
       <c r="CO14" t="n">
         <v>-0</v>
@@ -8109,13 +8109,13 @@
         <v>-0</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.01635127963026872</v>
+        <v>0.2528874134257927</v>
       </c>
       <c r="CR14" t="n">
-        <v>-0.0540555691439233</v>
+        <v>0.1162193615301228</v>
       </c>
       <c r="CS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT14" t="n">
         <v>0</v>
@@ -8127,7 +8127,7 @@
         <v>-0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.03798965313096233</v>
+        <v>-0.1946429791491124</v>
       </c>
       <c r="CX14" t="n">
         <v>0</v>
@@ -8136,10 +8136,10 @@
         <v>0</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.005311105464013206</v>
+        <v>0.002203060703730397</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.02437900009412021</v>
+        <v>0.128581418956033</v>
       </c>
       <c r="DB14" t="n">
         <v>0</v>
@@ -8154,34 +8154,34 @@
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>-0.03008671881153499</v>
+        <v>-0.08290390003201333</v>
       </c>
       <c r="DG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH14" t="n">
         <v>-0</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.0846566539949633</v>
+        <v>-0.1964315992440358</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.01629603818729655</v>
+        <v>0.03519065800207725</v>
       </c>
       <c r="DK14" t="n">
         <v>0</v>
       </c>
       <c r="DL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.00874622247519332</v>
+        <v>-0.07495130854173999</v>
       </c>
       <c r="DP14" t="n">
         <v>0</v>
@@ -8190,25 +8190,25 @@
         <v>0</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.0241571508726516</v>
+        <v>0.04401229807229912</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.004733682220515316</v>
+        <v>0.1553008671253669</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
         <v>-0</v>
       </c>
       <c r="DW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0.04080540800192708</v>
+        <v>-0.1833137485047188</v>
       </c>
       <c r="DY14" t="n">
         <v>-0</v>
@@ -8217,37 +8217,37 @@
         <v>-0</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.009928465526109447</v>
+        <v>-0.08211147931993908</v>
       </c>
       <c r="EB14" t="n">
-        <v>-0.004313268092767705</v>
+        <v>-0.02312522333280378</v>
       </c>
       <c r="EC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED14" t="n">
         <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
         <v>0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.0443123910977594</v>
+        <v>-0.02383379932494959</v>
       </c>
       <c r="EH14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI14" t="n">
         <v>-0</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.009214144144704065</v>
+        <v>-0.0347044476168711</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.02178922133024143</v>
+        <v>-0.04823617862177482</v>
       </c>
       <c r="EL14" t="n">
         <v>-0</v>
@@ -8262,7 +8262,7 @@
         <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0.03627471766878292</v>
+        <v>-0.1088431651110142</v>
       </c>
       <c r="EQ14" t="n">
         <v>-0</v>
@@ -8271,40 +8271,40 @@
         <v>-0</v>
       </c>
       <c r="ES14" t="n">
-        <v>-0.009948437523649793</v>
+        <v>-0.02525892889258948</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.02759587708631538</v>
+        <v>0.04316413867920667</v>
       </c>
       <c r="EU14" t="n">
         <v>0</v>
       </c>
       <c r="EV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX14" t="n">
         <v>0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.03923548980168945</v>
+        <v>-0.2357631999511348</v>
       </c>
       <c r="EZ14" t="n">
         <v>-0</v>
       </c>
       <c r="FA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB14" t="n">
-        <v>-0.001741497137267833</v>
+        <v>-0.004016884647356769</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.02170056017024585</v>
+        <v>0.1121515531277381</v>
       </c>
       <c r="FD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
         <v>0</v>
@@ -8313,10 +8313,10 @@
         <v>-0</v>
       </c>
       <c r="FG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0.01463236447843329</v>
+        <v>0.09213532179542021</v>
       </c>
       <c r="FI14" t="n">
         <v>0</v>
@@ -8325,10 +8325,10 @@
         <v>-0</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.02507839036728543</v>
+        <v>-0.01166517028949099</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.04223182923033963</v>
+        <v>0.2464454612475002</v>
       </c>
       <c r="FM14" t="n">
         <v>0</v>
@@ -8340,10 +8340,10 @@
         <v>0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.001433456347121325</v>
+        <v>-0.1183201383233434</v>
       </c>
       <c r="FR14" t="n">
         <v>-0</v>
@@ -8352,46 +8352,46 @@
         <v>-0</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.03244582343008491</v>
+        <v>0.3131015104153096</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.03419933776438701</v>
+        <v>-0.05094644359943281</v>
       </c>
       <c r="FV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
         <v>0</v>
       </c>
       <c r="FY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>-0.01726995570741145</v>
+        <v>-0.05879193227909165</v>
       </c>
       <c r="GA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0.02903915527028985</v>
+        <v>0.11556667679125</v>
       </c>
       <c r="GE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
